--- a/testcase/BoldSpec_Test_Case.xlsx
+++ b/testcase/BoldSpec_Test_Case.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -69,106 +69,6 @@
   </si>
   <si>
     <t>Duration(s)</t>
-  </si>
-  <si>
-    <t>TC_EDE_01</t>
-  </si>
-  <si>
-    <t>QA</t>
-  </si>
-  <si>
-    <t>End to End Order</t>
-  </si>
-  <si>
-    <t>Verify user able to place an order</t>
-  </si>
-  <si>
-    <t>Open the site
-Click on the Account icon on the header
-And Click on Login
-Login as customer
-Navigate to Home page
-Select cateogry from the header
-Click on first product 
-Navigate to product details page
-Add the product to cart
-Mini cart will open and look for go to checkout button
-Click on go to checkout on the right slide bar
-Go to checkout
-Accept the terms and conditions
-Select payement method
-Select Shipping method
-Click on submit order
-Observe the order confirmation screen</t>
-  </si>
-  <si>
-    <t>Category: Shop by Material, 
-Payment Method:Cash on delivery, 
-Shipping method: Standard</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Functional</t>
-  </si>
-  <si>
-    <t>User successfully completed checkout and reached order confirmation screen.</t>
-  </si>
-  <si>
-    <t>locator.click: Target page, context or browser has been closed</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>9/4/2026, 10:50:15 AM</t>
-  </si>
-  <si>
-    <t>9/4/2026, 10:50:23 AM</t>
-  </si>
-  <si>
-    <t>TC_EDE_02</t>
-  </si>
-  <si>
-    <t>Register</t>
-  </si>
-  <si>
-    <t>Verify user able to create an account</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open the site
-Click on the Account icon on the header
-Click on SignUp
-Select Salutation, Enter valid values for First Name, Last Name, Email Address, Password (minimum 8 characters), Street Address, Postal Code, City, choose Country &amp; State
-Then click on continue
-Observe the Account dash board is displayed.
-</t>
-  </si>
-  <si>
-    <t>Salutation: Mr.
-First name: Arizon
-Last name: Account
-Email address: Register@gmail.com
-Password: Pass@123
-Your address: Home Address
-Street address: 123 Main Street
-Postal code: 10001
-City: New York
-Country: United States
-State: New York</t>
-  </si>
-  <si>
-    <t>Account should be registered and user should land on the my accounts page</t>
-  </si>
-  <si>
-    <t>locator.selectOption: Target page, context or browser has been closed</t>
-  </si>
-  <si>
-    <t>9/4/2026, 10:50:25 AM</t>
-  </si>
-  <si>
-    <t>9/4/2026, 10:50:27 AM</t>
   </si>
 </sst>
 </file>
@@ -181,7 +81,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,13 +138,6 @@
       <color theme="1"/>
       <name val="Cambria"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -715,148 +608,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1273,92 +1166,36 @@
       <c r="Z1" s="6"/>
     </row>
     <row r="2" ht="262.2" customHeight="1" spans="1:26">
-      <c r="A2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" s="7">
-        <v>7.68</v>
-      </c>
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
     </row>
     <row r="3" ht="146" customHeight="1" spans="1:26">
-      <c r="A3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="N3" s="8">
-        <v>1.73</v>
-      </c>
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
